--- a/Regelsæt.xlsx
+++ b/Regelsæt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\RPA\Leverancer\Kontrol af betalings- og handlekommune\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\RPA\Leverancer\Kontrol af betalings- og handlekommune\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85879B04-8DDF-4234-9E44-E52A1A72627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C429A6-75A1-44DA-B38B-6274EC882696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organisationer" sheetId="1" r:id="rId1"/>
@@ -25,44 +25,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Børn</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Ungerådgivningen Special - Kompensation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>CFU Familierådgivningen - Rådgivere</t>
-  </si>
-  <si>
-    <t>CFU Familierådgivningen</t>
-  </si>
-  <si>
     <t>Organisation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Forebyggende Indsatser</t>
   </si>
   <si>
@@ -70,6 +40,27 @@
   </si>
   <si>
     <t>Voksenrådgivningen § 100</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 1</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 2</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 3</t>
+  </si>
+  <si>
+    <t>Familierådgivningen</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen Social 1 - Vagt &amp; Visitation</t>
+  </si>
+  <si>
+    <t>Social og jobrådgivningen</t>
+  </si>
+  <si>
+    <t>Specialenheden</t>
   </si>
 </sst>
 </file>
@@ -396,85 +387,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
